--- a/config/excel/upgrades.xlsx
+++ b/config/excel/upgrades.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="upgrades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,21 +423,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,37 +473,62 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>is_pet</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>max_level</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>once_per_run</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>once_per_chapter</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>apply_type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>apply_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>trigger_condition</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>effect_pack</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>effect_name</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>icon_file</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fx_below_monsters</t>
         </is>
       </c>
     </row>
@@ -528,30 +558,46 @@
           <t>增加20%气力</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>9</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>ki_mult</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>1.2</v>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/luck.png</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>multi_dart</t>
+          <t>multi_bullet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>多重飞镖</t>
+          <t>多重子弹</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -561,48 +607,66 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>🎯</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>普攻飞镖数量+1</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
+          <t>普攻子弹数量+1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>dart_count</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>bullet_count</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>effects/3.Gothicvania Magic Pack N2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>dart</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/multi_bullet.png</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>giant_dart</t>
+          <t>shuriken</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>巨大飞镖</t>
+          <t>手里剑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -612,150 +676,192 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>⭕</t>
+          <t>🎯</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>普攻20%概率发射巨大飞镖</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+          <t>每次连击释放2枚手里剑</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>9</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>giant_dart_chance</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>shuriken_count</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>combo_hit</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>effects/3.Gothicvania Magic Pack N2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>giant_dart</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>shuriken</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/shuriken.png</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ice_dart</t>
+          <t>bounce_bullet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>寒冰飞镖</t>
+          <t>弹射子弹</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>❄️</t>
+          <t>🔁</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>普攻命中5%释放寒冰飞镖</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
+          <t>普攻子弹在敌人间弹射（每级+1次）</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ice_dart_chance</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>0.05</v>
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>effects/2.Gothicvania Magic Pack N3</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ice</t>
-        </is>
-      </c>
+          <t>bounce_bullet</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>effects/5.GothicVania Magic Pack 5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/bounce_bullet.png</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>spirit_bomb</t>
+          <t>four_leaf_clover</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>元气弹</t>
+          <t>四叶草</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>💫</t>
+          <t>🍀</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>飞镖变元气弹</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+          <t>幸运提升（蓝-4%/级，紫+3%/级，橙+1%/级）</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>spirit_bomb</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>effects/10.GothicVania Magic Pack 7</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>spirit_bomb</t>
-        </is>
-      </c>
+          <t>luck_roll</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/four_leaf_clover.png</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>shuriken</t>
+          <t>godspeed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>手里剑</t>
+          <t>神速</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -765,150 +871,192 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>🎯</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>每次连击释放2枚手里剑</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+          <t>攻速×1.3/级，气力回复×0.85/级</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>9</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>shuriken_count</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>combo_hit</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>effects/3.Gothicvania Magic Pack N2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>shuriken</t>
-        </is>
-      </c>
+          <t>godspeed</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/godspeed.png</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>multi_combo</t>
+          <t>laser_blast</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>多重连击</t>
+          <t>激光冲击</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>连击次数×1.2倍</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
+          <t>普攻6%概率释放激光（每级+6%）</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>9</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>combo_mult</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>laser_blast</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>effects/custom/laser-blast</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>laser_blast</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/laser_blast.png</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>healing_combo</t>
+          <t>holy_shield</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>愈合连击</t>
+          <t>圣盾</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>🌿</t>
+          <t>🛡️</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>连击每+15释放藤蔓，回复5%生命</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+          <t>每5秒获得1层护盾</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>9</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>heal_pct</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>combo_milestone_15</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>effects/4.Gothicvania Magic Pack N4</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>vine</t>
-        </is>
-      </c>
+          <t>holy_shield_interval</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>effects/5.Gothicvania Magic Pack N5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/holy_shield.png</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>holy_shield</t>
+          <t>lightning_chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>圣盾</t>
+          <t>闪电链</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -918,313 +1066,405 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>🛡️</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>每5秒获得1层护盾</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
+          <t>连击每+8释放闪电链</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>combo_skill</t>
+        </is>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>9</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>holy_shield_interval</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>passive</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>effects/5.Gothicvania Magic Pack N5</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>shield</t>
-        </is>
-      </c>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>combo_milestone_8</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>effects/8.Gothicvania Magic Pack N8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/lightning_chain.png</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vampire_bat</t>
+          <t>bullet_burn</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>吸血蝙蝠</t>
+          <t>子弹灼烧</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>🦇</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>每击杀10敌人，蝙蝠群攻并回复2%生命</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
+          <t>普攻命中附加1.5秒灼烧DOT（每级提高灼烧伤害）</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>heal_pct</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kill_10</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>effects/6.Gothicvania Magic Pack N6</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>bat</t>
-        </is>
-      </c>
+          <t>bullet_burn</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>fire_pillar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/bullet_burn.png</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>meat_shield</t>
+          <t>desperate_counter</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>变肉</t>
+          <t>绝境反击</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>🛡️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>最大生命+10%，体积+15%</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+          <t>受击后4秒内攻速+20%与暴击率+20%（每级额外+5%）</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>9</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>hp_mult</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>desperate_counter</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>air_slash</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/desperate_counter.png</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>super_heal</t>
+          <t>steadfast_guard</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>超级治疗</t>
+          <t>不动如山</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>⛰️</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>所有回血效果+50%</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+          <t>站立1.5秒后生成减伤环，移动后消失；减伤30%（每级额外+5%，上限60%）</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>9</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>heal_bonus</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>effects/7.Gothicvania Magic Pack N7</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>heal</t>
-        </is>
-      </c>
+          <t>steadfast_guard</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/steadfast_guard.png</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lightning_chain</t>
+          <t>water_tornado</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>闪电链</t>
+          <t>水龙卷术</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>🌊</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>连击每+5释放闪电链</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+          <t>暴击+5%，连击每+5释放水龙卷</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>combo_skill</t>
+        </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>9</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>crit_rate</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>combo_milestone_5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>effects/8.Gothicvania Magic Pack N8</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>lightning</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>effects/13.Gothicvania Magic Pack 8/Magic Pack 8 files/sprites</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>tornado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/water_tornado.png</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shadow_clone</t>
+          <t>black_hole</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>影分身</t>
+          <t>黑洞</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>👤</t>
+          <t>🕳️</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>连击&gt;10召唤影分身</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
+          <t>连击8时生成黑洞</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>combo_skill</t>
+        </is>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>9</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>clone</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>combo_gt_10</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>effects/9.Gothicvania Magic Pack N9</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>clone</t>
-        </is>
+          <t>black_hole</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>combo_eq_8</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>effects/10.GothicVania Magic Pack 7/Magic Pack 7 files/sprites/vfx-d</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>black_hole</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/black_hole.png</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>water_tornado</t>
+          <t>blade_whirl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>水龙卷术</t>
+          <t>刀阵旋风</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1234,53 +1474,70 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>🌊</t>
+          <t>🌀</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>暴击+5%，连击每+3释放水龙卷</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
+          <t>连击每+8释放刀阵旋风</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>combo_skill</t>
+        </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>9</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>crit_rate</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>combo_milestone_3</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>effects/13.Gothicvania Magic Pack 8/Magic Pack 8 files/sprites</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>tornado</t>
-        </is>
-      </c>
+          <t>whirl</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>combo_milestone_8</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>effects/6.GothicVania Magic Pack 6/Magic Pack 6/sprites/slash-e</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>slash_e</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/blade_whirl.png</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>black_hole</t>
+          <t>charge_strike</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>黑洞</t>
+          <t>蓄力击</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1290,53 +1547,62 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>🕳️</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>连击8时生成黑洞</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+          <t>原地越久，普攻攻速与划线斩击伤害越高；斩击后重置</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>9</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>black_hole</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>combo_eq_8</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>effects/11.Warped Explosions Pack 6</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>black_hole</t>
-        </is>
-      </c>
+          <t>charge_strike</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>effects/2.Gothicvania Magic Pack N2 - Fire/Magic Pack Fire files/sprites/flame-loop</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>flame_loop</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/charge_strike.png</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>blade_whirl</t>
+          <t>abyss_explosion</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>刀阵旋风</t>
+          <t>深渊爆炸</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1346,109 +1612,131 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>🌀</t>
+          <t>💣</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>连击每+5释放刀阵旋风</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+          <t>画线闭合圆时在范围内爆炸（每级伤害×1.2）</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>9</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>whirl</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>combo_milestone_5</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>effects/12.Gothicvania Magic Pack 8</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>whirl</t>
-        </is>
-      </c>
+          <t>abyss_explosion</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>effects/9.Warped Explosion Pack 5/Explosions Pack 5 Files/sprites/explosion-c</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>explosion_c</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/abyss_explosion.png</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>great_fireball</t>
+          <t>mirror_bullet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>豪火球术</t>
+          <t>镜像子弹</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🪞</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>连击每+10释放豪火球</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
+          <t>普攻子弹命中后返回主角，回程可伤害敌人</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>fireball</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>combo_milestone_10</t>
-        </is>
+      <c r="J19" t="n">
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>effects/1.Gothicvania Magic Pack N1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>fireball</t>
-        </is>
-      </c>
+          <t>mirror_bullet</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>effects/5.GothicVania Magic Pack 5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/mirror_bullet.png</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>heavenly_thunder</t>
+          <t>multi_combo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>天雷</t>
+          <t>多重连击</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1458,155 +1746,180 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>每秒落雷范围攻击</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+          <t>连击次数每级+0.2权重</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>9</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>thunder</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>passive_1s</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>effects/8.Gothicvania Magic Pack N8</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>thunder</t>
-        </is>
-      </c>
+          <t>combo_mult</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/multi_combo.png</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wild_wolf</t>
+          <t>close_range_shot</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>野狼</t>
+          <t>近距离射击</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>🐺</t>
+          <t>🎯</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>宠物：召唤一只野狼</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
+          <t>普攻子弹飞行距离越短伤害越高（每级提高距离系数）</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>9</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>pet_wolf</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Characters/Characters(100x100)/Werewolf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Werewolf</t>
-        </is>
-      </c>
+          <t>close_range_shot</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/close_range_shot.png</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>wild_bull</t>
+          <t>wild_call</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>野牛</t>
+          <t>野性号召</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>🐂</t>
+          <t>📯</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>宠物：召唤一只野牛</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
+          <t>每有1个召唤物，主角攻速+6%（每级额外+2%）</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>9</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>pet_bull</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Characters/Characters(100x100)/Werebear</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Werebear</t>
-        </is>
-      </c>
+          <t>wild_call</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/wild_call.png</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>divine_god</t>
+          <t>bloodthirst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>天神</t>
+          <t>嗜血</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1616,79 +1929,832 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🩸</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>宠物：召唤天神</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
+          <t>召唤物命中有8%概率为主角回复1%生命</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>pet_god</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Characters/Characters(100x100)/Knight Templar</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Knight Templar</t>
-        </is>
-      </c>
+          <t>bloodthirst</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/bloodthirst.png</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>adversity_heart</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>逆境之心</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>生命低于50%时攻击+15%（每级额外+5%）</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adversity_heart</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/adversity_heart.png</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>barrage_king</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>弹幕之王</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>👑</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>普攻子弹数量+3，攻速×0.8（本章一次）</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>barrage_king</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/barrage_king.png</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>stillness_heart</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>静止之心</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>💠</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>原地时每0.5秒增加3%暴击与3%暴伤，最多15层；移动后保留3秒（本章一次）</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>stillness_heart</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/stillness_heart.png</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>spirit_bomb</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>元气弹</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>💫</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>普攻变为元气弹，伤害+30%（本局一次）</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>spirit_bomb</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>effects/3.Gothicvania Magic Pack N3/Magic Pack 3 files/sprites/small-spark-3</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>spirit_bomb</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/spirit_bomb.png</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>great_fireball</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>豪火球术</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>连击每+12释放豪火球</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>combo_skill</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>combo_milestone_12</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>great_fireball_pixel</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/great_fireball.png</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>heavenly_thunder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>天雷</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>每秒落雷范围攻击</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>thunder</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>passive_1s</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>effects/8.Gothicvania Magic Pack N8</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>thunder</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/heavenly_thunder.png</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>nurturing_heart</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>养育之心</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>💗</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>宠物数量翻倍</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>宠物数量翻倍（本章一次）</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>pet_mult</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/nurturing_heart.png</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>穿透</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>➡️</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>普攻子弹穿透敌人（本局一次）</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>pierce_bullet</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>effects/5.GothicVania Magic Pack 5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>auto_bullet</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/pierce.png</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>super_mushroom</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>超级蘑菇</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>🍄</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>斩击伤害×1.3，回满血，最大生命×1.2，体型×1.5（本局一次）</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>super_mushroom</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/super_mushroom.png</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>wild_wolf</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>狼战士</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>🐺</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>宠物：召唤两名狼战士</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
         <v>9</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>pet_mult</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>pet_wolf</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>2</v>
       </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Characters/Characters(100x100)/Werewolf</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Werewolf</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/wild_wolf.png</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>wild_bull</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>野熊</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>🐂</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>宠物：召唤一只野熊</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>pet_bull</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Characters/Characters(100x100)/Werebear</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Werebear</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/wild_bull.png</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>divine_god</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>天神</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>宠物：召唤天神</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>pet_god</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Characters/Characters(100x100)/Knight Templar</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Knight Templar</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>res://assets/icons/upgrades/divine_god.png</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
